--- a/SCRAPING/tempat-makan_empty_updated.xlsx
+++ b/SCRAPING/tempat-makan_empty_updated.xlsx
@@ -6729,21 +6729,43 @@
           <t>https://www.google.com/maps/place/Warung+Kanggo+Riko/data=!4m7!3m6!1s0x2e78a1f40355872b:0xe4f19e39c97b56d5!8m2!3d-8.1875064!4d112.5293143!16s%2Fg%2F11hbfdkf40!19sChIJK4dVA_SheC4R1VZ7yTme8eQ?authuser=0&amp;hl=id&amp;rclk=1</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Sego Pecel</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>7000</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Sego Lalapan</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M107" t="n">
+        <v>7000</v>
+      </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Menu Tidak Terdeteksi. Preview text: ['']</t>
+          <t>Sukses</t>
         </is>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
-      </c>
-      <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="inlineStr"/>
+        <v>7000</v>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>GrabFood</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>https://gofood.co.id/malang/restaurant/warung-jowo-kanggo-riko-wagir-3a6f43dd-baa6-4d99-957a-45f869bbe7aa</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6776,21 +6798,43 @@
           <t>https://www.google.com/maps/place/Depot+Rahmad/data=!4m7!3m6!1s0x2dd61f201718313d:0xc4509089a65de46e!8m2!3d-8.169779!4d112.6928619!16s%2Fg%2F11hb31n7s2!19sChIJPTEYFyAf1i0RbuRdpomQUMQ?authuser=0&amp;hl=id&amp;rclk=1</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Telur Mata Sapi</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Gurami Asam Manis</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>82000</v>
+      </c>
+      <c r="M108" t="n">
+        <v>12500</v>
+      </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Menu Tidak Terdeteksi. Preview text: ['']</t>
+          <t>Sukses</t>
         </is>
       </c>
       <c r="O108" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="inlineStr"/>
+        <v>12500</v>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>GrabFood</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>https://gofood.co.id/malang/restaurant/depot-rahmad-special-nasi-goreng-chinese-food-turen-3f75cbe3-eecd-4679-b868-ceb50e63a087</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6823,21 +6867,43 @@
           <t>https://www.google.com/maps/place/Mahoni+Cafe+Resto/data=!4m7!3m6!1s0x2e78a16f555eab03:0xd281ade96a98ced3!8m2!3d-8.1890806!4d112.5287882!16s%2Fg%2F11ptv6hswr!19sChIJA6teVW-heC4R086YaumtgdI?authuser=0&amp;hl=id&amp;rclk=1</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Es Teh</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Rujak Cingur Bu Murti Ngaglik</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>22000</v>
+      </c>
+      <c r="M109" t="n">
+        <v>11250</v>
+      </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>Menu Tidak Terdeteksi. Preview text: ['']</t>
+          <t>Sukses</t>
         </is>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
-      </c>
-      <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="inlineStr"/>
+        <v>11250</v>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>GrabFood</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>https://gofood.co.id/malang/restaurant/kedai-mahoni-jl-kasiman-37-ngaglik-fd2ead62-4c72-49e4-97c6-878102bc07d8</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6877,13 +6943,17 @@
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
         <is>
-          <t>Menu Tidak Terdeteksi. Preview text: ['']</t>
+          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Link GrabFood Tidak Ditemukan</t>
         </is>
       </c>
       <c r="O110" t="n">
-        <v>0</v>
-      </c>
-      <c r="P110" t="inlineStr"/>
+        <v>25000</v>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Estimasi Cerdas</t>
+        </is>
+      </c>
       <c r="Q110" t="inlineStr"/>
     </row>
     <row r="111">
@@ -6917,21 +6987,43 @@
           <t>https://www.google.com/maps/place/Warung+Lesehan+Ikan+Tawar+Segar+Dempok/data=!4m7!3m6!1s0x2e78a1f415712e43:0xcf400b5450da5190!8m2!3d-8.1887371!4d112.5279496!16s%2Fg%2F11g9vr402r!19sChIJQy5xFfSheC4RkFHaUFQLQM8?authuser=0&amp;hl=id&amp;rclk=1</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>cumi cumi</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>36500</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>kemasan 500 gr frozzen</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>36500</v>
+      </c>
+      <c r="M111" t="n">
+        <v>36500</v>
+      </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>Menu Tidak Terdeteksi. Preview text: ['']</t>
+          <t>Sukses</t>
         </is>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
-      </c>
-      <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="inlineStr"/>
+        <v>36500</v>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>GrabFood</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>https://gofood.co.id/malang/restaurant/ikan-segar-malang-kedungkandang-699a5274-9c49-43eb-acac-862e0f015144</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -6964,21 +7056,43 @@
           <t>https://www.google.com/maps/place/Warung+Bu+Warsi+Dempok/data=!4m7!3m6!1s0x2e78a1d75d43f669:0x4ab9f63f973beaca!8m2!3d-8.1879433!4d112.5291724!16s%2Fg%2F11ptzq8q4r!19sChIJafZDXdeheC4Ryuo7lz_2uUo?authuser=0&amp;hl=id&amp;rclk=1</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Es Coffi Mix</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Nasi + Sambel Goreng + Paru</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>23000</v>
+      </c>
+      <c r="M112" t="n">
+        <v>17000</v>
+      </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>Menu Tidak Terdeteksi. Preview text: ['']</t>
+          <t>Sukses</t>
         </is>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
-      </c>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr"/>
+        <v>17000</v>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>GrabFood</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>https://gofood.co.id/solo/restaurant/warung-makan-bu-warsi-f53107a0-ff9d-4563-b89e-8a01c2f7791e</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">

--- a/SCRAPING/tempat-makan_empty_updated.xlsx
+++ b/SCRAPING/tempat-makan_empty_updated.xlsx
@@ -553,15 +553,15 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: ['Beranda', 'GoFood HEMAT', 'Baru', 'Cara hemat ngeGoFood. Harga termasuk ongkir, tanpa syarat!', 'Rekomendasi', 'Masuk', 'Beranda', '/', 'Malang', '/'] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -626,7 +626,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1087,15 +1087,15 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: ['Beranda', 'GoFood HEMAT', 'Baru', 'Cara hemat ngeGoFood. Harga termasuk ongkir, tanpa syarat!', 'Rekomendasi', 'Masuk', 'Kasembon', 'Cari yang enak di sini, dari resto dengan rating jempolan sampai hidangan legendaris.', 'Beranda', '/'] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1207,15 +1207,15 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>GoFood: Link GoFood Tidak Ditemukan | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
@@ -1258,15 +1258,15 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: ['Beranda', 'GoFood HEMAT', 'Baru', 'Cara hemat ngeGoFood. Harga termasuk ongkir, tanpa syarat!', 'Rekomendasi', 'Masuk', 'Beranda', '/', 'Malang', '/'] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1654,15 +1654,15 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
@@ -1705,15 +1705,15 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr"/>
@@ -1756,15 +1756,15 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Menu GrabFood Tidak Terdeteksi. Preview: ['Masuk/Daftar', 'ID', 'Selamat Siang', 'Makanannya mau diantar ke mana hari ini?', 'Cari', 'Pasti ada sesuatu buat tiap orang!', 'Sate', 'Hidangan Laut', 'Bubble Tea', 'Hidangan Jepang']</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr"/>
@@ -1807,15 +1807,15 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: ['Beranda', 'GoFood HEMAT', 'Baru', 'Cara hemat ngeGoFood. Harga termasuk ongkir, tanpa syarat!', 'Rekomendasi', 'Masuk', 'Rekomendasi Malang', 'Eksplor kumpulan rekomendasi yang kami buat untuk berbagai kebutuhanmu', 'Beranda', '/'] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr"/>
@@ -1858,15 +1858,15 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr"/>
@@ -1909,15 +1909,15 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>GoFood: Link GoFood Tidak Ditemukan | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr"/>
@@ -1960,15 +1960,15 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>GoFood: Link GoFood Tidak Ditemukan | GrabFood: Menu GrabFood Tidak Terdeteksi. Preview: ['Masuk/Daftar', 'ID', 'Selamat Siang', 'Makanannya mau diantar ke mana hari ini?', 'Cari', 'Pasti ada sesuatu buat tiap orang!', 'Camilan Cepat', 'Asli Indonesia 🇮🇩', 'Ayam', 'Burger']</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr"/>
@@ -2011,15 +2011,15 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Menu GrabFood Tidak Terdeteksi. Preview: ['Masuk/Daftar', 'ID', 'Selamat Siang', 'Makanannya mau diantar ke mana hari ini?', 'Cari', 'Pasti ada sesuatu buat tiap orang!', 'Minuman', 'Masakan Barat', 'Asli Indonesia 🇮🇩', 'Mie']</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr"/>
@@ -2062,15 +2062,15 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>GoFood: Link GoFood Tidak Ditemukan | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr"/>
@@ -2113,15 +2113,15 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: ['Beranda', 'GoFood HEMAT', 'Baru', 'Cara hemat ngeGoFood. Harga termasuk ongkir, tanpa syarat!', 'Rekomendasi', 'Masuk', 'Beranda', '/', 'Malang', '/'] | GrabFood: Menu GrabFood Tidak Terdeteksi. Preview: ['Masuk/Daftar', 'ID', 'Selamat Siang', 'Makanannya mau diantar ke mana hari ini?', 'Cari', 'Pasti ada sesuatu buat tiap orang!', 'Makanan Cepat Saji', 'Sate', 'Ayam Goreng', 'Asli Indonesia 🇮🇩']</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr"/>
@@ -2164,15 +2164,15 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: ['Beranda', 'GoFood HEMAT', 'Baru', 'Cara hemat ngeGoFood. Harga termasuk ongkir, tanpa syarat!', 'Rekomendasi', 'Masuk', 'Ngantang', 'Cari yang enak di sini, dari resto dengan rating jempolan sampai hidangan legendaris.', 'Beranda', '/'] | GrabFood: Menu GrabFood Tidak Terdeteksi. Preview: ['Masuk/Daftar', 'ID', 'Selamat Malam', 'Makanannya mau diantar ke mana hari ini?', 'Cari', 'Pasti ada sesuatu buat tiap orang!', 'Mie', 'Nasi Goreng', 'Hidangan Jepang', 'Bakso']</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr"/>
@@ -2215,15 +2215,15 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr"/>
@@ -2266,15 +2266,15 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>GoFood: Link GoFood Tidak Ditemukan | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr"/>
@@ -2317,15 +2317,15 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: ['Beranda', 'GoFood HEMAT', 'Baru', 'Cara hemat ngeGoFood. Harga termasuk ongkir, tanpa syarat!', 'Rekomendasi', 'Masuk', 'Ngantang', 'Cari yang enak di sini, dari resto dengan rating jempolan sampai hidangan legendaris.', 'Beranda', '/'] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr"/>
@@ -2368,15 +2368,15 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr"/>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -2902,15 +2902,15 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: GrabFood Halaman Kosong (Lokasi Butuh Diatur)</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr"/>
@@ -2953,15 +2953,15 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr"/>
@@ -3004,15 +3004,15 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Menu GrabFood Tidak Terdeteksi. Preview: ['Masuk/Daftar', 'ID', 'Selamat Malam', 'Makanannya mau diantar ke mana hari ini?', 'Cari', 'Pasti ada sesuatu buat tiap orang!', 'Kopi', 'Masakan Barat', 'Asli Indonesia 🇮🇩', 'Chinese']</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr"/>
@@ -3055,15 +3055,15 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Menu GrabFood Tidak Terdeteksi. Preview: ['Masuk/Daftar', 'ID', 'Selamat Malam', 'Makanannya mau diantar ke mana hari ini?', 'Cari', 'Pasti ada sesuatu buat tiap orang!', 'Hidangan Laut', 'Bakso', 'Ayam', 'Makanan Cepat Saji']</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr"/>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -3175,15 +3175,15 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: ['Beranda', 'GoFood HEMAT', 'Baru', 'Cara hemat ngeGoFood. Harga termasuk ongkir, tanpa syarat!', 'Rekomendasi', 'Masuk', 'Malang', 'Cari yang enak di sini, dari resto dengan rating jempolan sampai hidangan legendaris.', 'Beranda', '/'] | GrabFood: Menu GrabFood Tidak Terdeteksi. Preview: ['Masuk/Daftar', 'ID', 'Selamat Malam', 'Makanannya mau diantar ke mana hari ini?', 'Cari', 'Pasti ada sesuatu buat tiap orang!', 'Minuman', 'Nasi Goreng', 'Ayam Goreng', 'Ayam']</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr"/>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -3295,15 +3295,15 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: ['Beranda', 'GoFood HEMAT', 'Baru', 'Cara hemat ngeGoFood. Harga termasuk ongkir, tanpa syarat!', 'Rekomendasi', 'Masuk', 'Beranda', '/', 'Malang', '/'] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr"/>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -3622,15 +3622,15 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>GoFood: Link GoFood Tidak Ditemukan | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O53" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr"/>
@@ -3673,15 +3673,15 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O54" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr"/>
@@ -3724,15 +3724,15 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O55" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr"/>
@@ -3844,15 +3844,15 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O57" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr"/>
@@ -3895,15 +3895,15 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: ['Beranda', 'GoFood HEMAT', 'Baru', 'Cara hemat ngeGoFood. Harga termasuk ongkir, tanpa syarat!', 'Rekomendasi', 'Masuk', 'Beranda', '/', 'Malang', '/'] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O58" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr"/>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -4084,15 +4084,15 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: ['Beranda', 'GoFood HEMAT', 'Baru', 'Cara hemat ngeGoFood. Harga termasuk ongkir, tanpa syarat!', 'Rekomendasi', 'Masuk', 'Beranda', '/', 'Malang', '/'] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O61" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr"/>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -4480,15 +4480,15 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>GoFood: Link GoFood Tidak Ditemukan | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O67" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr"/>
@@ -4531,15 +4531,15 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: ['Beranda', 'GoFood HEMAT', 'Baru', 'Cara hemat ngeGoFood. Harga termasuk ongkir, tanpa syarat!', 'Rekomendasi', 'Masuk', 'Beranda', '/', 'Malang', '/'] | GrabFood: Menu GrabFood Tidak Terdeteksi. Preview: ['Masuk/Daftar', 'ID', 'Selamat Malam', 'Makanannya mau diantar ke mana hari ini?', 'Cari', 'Pasti ada sesuatu buat tiap orang!', 'Ayam', 'Hidangan Jepang', 'Chinese', 'Minuman']</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O68" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr"/>
@@ -4582,15 +4582,15 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>GoFood: Link GoFood Tidak Ditemukan | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O69" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr"/>
@@ -4633,15 +4633,15 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Menu GrabFood Tidak Terdeteksi. Preview: ['Masuk/Daftar', 'ID', 'Selamat Malam', 'Makanannya mau diantar ke mana hari ini?', 'Cari', 'Pasti ada sesuatu buat tiap orang!', 'Roti &amp; Kue', 'Asli Indonesia 🇮🇩', 'Masakan Barat', 'Ayam Goreng']</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O70" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr"/>
@@ -4684,15 +4684,15 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O71" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr"/>
@@ -4735,15 +4735,15 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O72" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr"/>
@@ -4786,15 +4786,15 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O73" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr"/>
@@ -4837,15 +4837,15 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O74" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr"/>
@@ -4888,15 +4888,15 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: GrabFood Halaman Kosong (Lokasi Butuh Diatur)</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O75" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr"/>
@@ -4939,15 +4939,15 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Menu GrabFood Tidak Terdeteksi. Preview: ['Masuk/Daftar', 'ID', 'Selamat Malam', 'Makanannya mau diantar ke mana hari ini?', 'Cari', 'Pasti ada sesuatu buat tiap orang!', 'Roti &amp; Kue', 'Chinese', 'Camilan Cepat', 'Hidangan Jepang']</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O76" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr"/>
@@ -4990,15 +4990,15 @@
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O77" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr"/>
@@ -5041,15 +5041,15 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Menu GrabFood Tidak Terdeteksi. Preview: ['Masuk/Daftar', 'ID', 'Selamat Malam', 'Makanannya mau diantar ke mana hari ini?', 'Cari', 'Pasti ada sesuatu buat tiap orang!', 'Ayam Goreng', 'Roti &amp; Kue', 'Hidangan Jepang', 'Cemilan']</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O78" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr"/>
@@ -5092,15 +5092,15 @@
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O79" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr"/>
@@ -5143,15 +5143,15 @@
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O80" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr"/>
@@ -5194,15 +5194,15 @@
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
-          <t>GoFood: Link GoFood Tidak Ditemukan | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O81" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr"/>
@@ -5245,15 +5245,15 @@
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: ['Beranda', 'GoFood HEMAT', 'Baru', 'Cara hemat ngeGoFood. Harga termasuk ongkir, tanpa syarat!', 'Rekomendasi', 'Masuk', 'Kromengan', 'Cari yang enak di sini, dari resto dengan rating jempolan sampai hidangan legendaris.', 'Beranda', '/'] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O82" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr"/>
@@ -5296,15 +5296,15 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: ['Beranda', 'GoFood HEMAT', 'Baru', 'Cara hemat ngeGoFood. Harga termasuk ongkir, tanpa syarat!', 'Rekomendasi', 'Masuk', 'Beranda', '/', 'Malang', '/'] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O83" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr"/>
@@ -5347,15 +5347,15 @@
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O84" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr"/>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
@@ -5674,15 +5674,15 @@
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: ['Beranda', 'GoFood HEMAT', 'Baru', 'Cara hemat ngeGoFood. Harga termasuk ongkir, tanpa syarat!', 'Rekomendasi', 'Masuk', 'Beranda', '/', 'Malang', '/'] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O89" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr"/>
@@ -5725,15 +5725,15 @@
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
-          <t>GoFood: Link GoFood Tidak Ditemukan | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O90" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr"/>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -5983,15 +5983,15 @@
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
-          <t>GoFood: Link GoFood Tidak Ditemukan | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O94" t="n">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr"/>
@@ -6034,15 +6034,15 @@
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Menu GrabFood Tidak Terdeteksi. Preview: ['Masuk/Daftar', 'ID', 'Selamat Malam', 'Makanannya mau diantar ke mana hari ini?', 'Cari', 'Pasti ada sesuatu buat tiap orang!', 'Ayam Goreng', 'Bubble Tea', 'Camilan Cepat', 'Masakan Barat']</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O95" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr"/>
@@ -6085,15 +6085,15 @@
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Menu GrabFood Tidak Terdeteksi. Preview: ['Masuk/Daftar', 'ID', 'Selamat Malam', 'Makanannya mau diantar ke mana hari ini?', 'Cari', 'Pasti ada sesuatu buat tiap orang!', 'Minuman', 'Bakso', 'Martabak', 'Asli Indonesia 🇮🇩']</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O96" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr"/>
@@ -6136,15 +6136,15 @@
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O97" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr"/>
@@ -6187,15 +6187,15 @@
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
-          <t>GoFood: Link GoFood Tidak Ditemukan | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O98" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr"/>
@@ -6238,15 +6238,15 @@
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
-          <t>GoFood: Link GoFood Tidak Ditemukan | GrabFood: Menu GrabFood Tidak Terdeteksi. Preview: ['Masuk/Daftar', 'ID', 'Selamat Malam', 'Makanannya mau diantar ke mana hari ini?', 'Cari', 'Pasti ada sesuatu buat tiap orang!', 'Cemilan', 'Hidangan Jepang', 'Bakso', 'Hidangan Laut']</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O99" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr"/>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -6358,15 +6358,15 @@
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
-          <t>GoFood: Link GoFood Tidak Ditemukan | GrabFood: Menu GrabFood Tidak Terdeteksi. Preview: ['Masuk/Daftar', 'ID', 'Selamat Malam', 'Makanannya mau diantar ke mana hari ini?', 'Cari', 'Pasti ada sesuatu buat tiap orang!', 'Ayam Goreng', 'Martabak', 'Roti &amp; Kue', 'Mie']</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O101" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr"/>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -6478,15 +6478,15 @@
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr">
         <is>
-          <t>GoFood: Link GoFood Tidak Ditemukan | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O103" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr"/>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
@@ -6943,15 +6943,15 @@
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
         <is>
-          <t>GoFood: Menu Tidak Terdeteksi. Preview text: [''] | GrabFood: Link GrabFood Tidak Ditemukan</t>
+          <t>Gagal (Estimasi Dihapus)</t>
         </is>
       </c>
       <c r="O110" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Estimasi Cerdas</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr"/>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>GrabFood</t>
+          <t>GoFood</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
